--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91562</v>
+        <v>91564</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91565</v>
+        <v>91571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -4682,7 +4682,7 @@
         <v>136501559</v>
       </c>
       <c r="B36" t="n">
-        <v>91571</v>
+        <v>91575</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
